--- a/results/MATCH_CONFIRMADO_6genes_Ensembl.xlsx
+++ b/results/MATCH_CONFIRMADO_6genes_Ensembl.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Genes_em_comum_VALIDADO" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GO_BP_confirmado" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KEGG_confirmado" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CORRECAO_direcao_concordancia" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Genes_em_comum_VALIDADO'!$A$1:$J$7</definedName>
@@ -26,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +57,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +80,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
         <bgColor rgb="00C6E0B4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+        <bgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -103,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -124,6 +136,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2231,4 +2247,395 @@
   <autoFilter ref="A1:H20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="19" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CORREÇÃO IMPORTANTE: direção de concordância entre SUI e POP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="10" t="inlineStr"/>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>O professor apontou (via INPP4B) que a direção mudou entre versões da análise. Investiguei a fundo: o log2FoldChange BRUTO do INPP4B nunca mudou de sinal em NENHUMA das 5 variantes de pipeline já rodadas (negativo no SUI, negativo no POP, sempre). O problema não é um bug de processamento de dados — é que usei DUAS convenções diferentes para rotular 'concordante/discordante' em scripts diferentes, e elas dão respostas opostas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="10" t="inlineStr"/>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Convenção A (sinal bruto — a que você e o Perplexity usaram, e que eu também usei nos scripts mais recentes 'match confirmado')</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="49" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Compara só se os dois log2FC têm o MESMO SINAL matemático, sem ajustar pela direção do contraste de cada experimento. Por essa convenção, os 6 genes SÃO 'mesma direção' (todos sobem em ambos, exceto INPP4B que desce em ambos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Convenção B (ajustada pela direção de doença — a que usei no primeiríssimo script deste projeto, para os 4 genes do pipeline com filtro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>O contraste do SUI é Treated vs Untreated (log2FC negativo = mais alto no Untreated). O contraste do POP é POP vs Controle (log2FC positivo = mais alto no POP/doença). Essas duas referências são OPOSTAS: no SUI, 'para cima na doença' é log2FC NEGATIVO; no POP, 'para cima na doença' é log2FC POSITIVO. Ajustando por isso, TODOS OS 6 GENES ficam 'discordantes' — inclusive os 5 que pareciam concordantes pela Convenção A.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="19" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>O problema de fundo (mais importante que a convenção em si)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="94" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Nenhuma das duas convenções é objetivamente 'a certa', porque o dataset de SUI NÃO TEM grupo controle saudável/não lesionado — só tem 'lesionado sem tratamento' (Untreated) vs. 'lesionado + hMSC' (Treated). Os dois grupos sofreram a MESMA lesão; a única diferença é receber ou não a terapia com células-tronco. Ou seja, é uma comparação de EFEITO DE TRATAMENTO, não de doença-vs-saudável — enquanto o POP é doença-vs-saudável de verdade. Comparar a 'direção' entre os dois exige uma suposição interpretativa (qual lado do SUI é análogo à doença) que é genuinamente discutível, não um fato objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="10" t="inlineStr"/>
+    </row>
+    <row r="14" ht="19" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Recomendação para o seu texto/professor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="49" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Reporte os log2FC e padj de cada gene em cada dataset SEPARADAMENTE (sem alegar 'concordância' como fato), e explique essa limitação estrutural do desenho do SUI (ausência de controle saudável) explicitamente — isso é honesto e mostra rigor metodológico, é exatamente o tipo de coisa que orientadores valorizam ver reconhecida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Human_Ortholog_Symbol</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>SUI_36h_log2FC</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>POP_log2FC</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>SUI_dir_bruto</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>POP_dir_bruto</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>mesma_direcao_bruta</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>SUI_dir_doenca</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>POP_dir_doenca</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Concordante_ajustado_por_doenca</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>KRT10</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>4.29965074695649</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>3.15384321636888</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>down_na_lesao</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>up_no_POP</t>
+        </is>
+      </c>
+      <c r="I18" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>INPP4B</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>-8.406033881756599</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>-0.963600802171815</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>down</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>up_na_lesao</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>down_no_POP</t>
+        </is>
+      </c>
+      <c r="I19" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>CWH43</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>10.617749169839</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>3.15948869426397</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>down_na_lesao</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>up_no_POP</t>
+        </is>
+      </c>
+      <c r="I20" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>SERPINB2</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>5.15827869192486</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>3.39689224183895</v>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>down_na_lesao</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>up_no_POP</t>
+        </is>
+      </c>
+      <c r="I21" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>CALML5</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>12.0427271777591</v>
+      </c>
+      <c r="C22" s="7" t="n">
+        <v>5.05799438469499</v>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>down_na_lesao</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>up_no_POP</t>
+        </is>
+      </c>
+      <c r="I22" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>DMKN</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>6.34644377429693</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>2.58498190233702</v>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>up</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>down_na_lesao</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>up_no_POP</t>
+        </is>
+      </c>
+      <c r="I23" s="11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>